--- a/stories/arbres/ATOM-LAN.SON.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Blanche s'assoit près de la fenêtre. Maman est là. Il pleut. Ça fait plic ploc. Maman dit : c'est un son. Quel nom ? Blanche dit : la pluie. Maman dit : oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Maman dit : encore un son. Quel nom ? Blanche dit : le train. Maman dit : oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Maman dit : un son. Quel nom ? Blanche dit : le chat. Le chat vient. Blanche le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+          <t>Blanche s'assoit près de la fenêtre. Maman est là. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Le chat vient. Blanche le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,22 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Blanche s'assoit près de la fenêtre. Maman est là. Il pleut. Ça fait plic ploc.
+maman|C'est un son. Quel nom ?
+enfant-f|La pluie.
+maman|Oui.
+narrateur|Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou.
+maman|Encore un son. Quel nom ?
+enfant-f|Le train.
+maman|Oui.
+narrateur|Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou.
+maman|Un son. Quel nom ?
+enfant-f|Le chat.
+narrateur|Le chat vient. Blanche le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Blanche entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Blanche a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le chat ronronne. Blanche pose la tête sur maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,7 @@
 narrateur|Le chat vient. Blanche le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Blanche entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Blanche a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Le chat ronronne. Blanche pose la tête sur maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blanche nomme les sons</t>
+          <t>Les chaussures mouillées d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ça sent la soupe. Les chaussures mouillées font une flaque. Aniss s'assoit, écoute, et nomme la pluie, le train, le chat.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Blanche s'assoit près de la fenêtre. Maman est là. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Le chat vient. Blanche le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+          <t>Ça sent la soupe près de la porte. Les chaussures mouillées font une petite flaque. Le tapis absorbe une goutte. La porte est encore froide. Une vapeur monte de la cuisine. Un manteau goutte sur le crochet. La capuche est lourde, toute sombre. Un gant a glissé près du paillasson. Tes chaussures sont mouillées, Aniss. On les laisse ici. Oui, maman. Elles font une flaque. La soupe est presque prête. Je vous entends d'ici. En ce moment, Aniss s'assoit près de la fenêtre. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Aniss le caresse. Le poil sent un peu la pluie. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Aniss. Tu as dit le nom. C'est du bon travail. Tu as fini d'écouter ? Encore un peu. La soupe attend. Le manteau goutte encore. Une goutte tombe sur le gant. Encore un petit son. La goutte. Oui. On nomme le son.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Blanche s'assoit près de la fenêtre. Maman est là. Il pleut. Ça fait plic ploc.
-maman|C'est un son. Quel nom ?
-enfant-f|La pluie.
+          <t>narrateur|Ça sent la soupe près de la porte.
+narrateur|Les chaussures mouillées font une petite flaque.
+narrateur|Le tapis absorbe une goutte.
+narrateur|La porte est encore froide.
+narrateur|Une vapeur monte de la cuisine.
+narrateur|Un manteau goutte sur le crochet.
+narrateur|La capuche est lourde, toute sombre.
+narrateur|Un gant a glissé près du paillasson.
+maman|Tes chaussures sont mouillées, Aniss.
+maman|On les laisse ici.
+enfant-m|Oui, maman.
+enfant-m|Elles font une flaque.
+papa|La soupe est presque prête.
+papa|Je vous entends d'ici.
+narrateur|En ce moment, Aniss s'assoit près de la fenêtre.
+narrateur|Il pleut.
+narrateur|Ça fait plic ploc.
+maman|C'est un son.
+maman|Quel nom ?
+enfant-m|La pluie.
 maman|Oui.
-narrateur|Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou.
-maman|Encore un son. Quel nom ?
-enfant-f|Le train.
+maman|Le nom du son, c'est la pluie.
+narrateur|Plus loin, un bruit long.
+narrateur|Tchou tchou.
+maman|Encore un son.
+maman|Quel nom ?
+enfant-m|Le train.
 maman|Oui.
-narrateur|Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou.
-maman|Un son. Quel nom ?
-enfant-f|Le chat.
-narrateur|Le chat vient. Blanche le caresse. Pluie. Train. Chat. On entend. On nomme le son.</t>
+maman|Le nom du son, c'est le train.
+narrateur|Puis, dans la pièce, un miaulement.
+narrateur|Miaou.
+maman|Un son.
+maman|Quel nom ?
+enfant-m|Le chat.
+maman|Oui.
+narrateur|Le chat vient.
+narrateur|Aniss le caresse.
+narrateur|Le poil sent un peu la pluie.
+maman|On entend.
+maman|On nomme le son.
+enfant-m|Pluie.
+enfant-m|Train.
+enfant-m|Chat.
+papa|Bravo, Aniss.
+papa|Tu as dit le nom.
+maman|C'est du bon travail.
+maman|Tu as fini d'écouter ?
+enfant-m|Encore un peu.
+papa|La soupe attend.
+narrateur|Le manteau goutte encore.
+narrateur|Une goutte tombe sur le gant.
+maman|Encore un petit son.
+enfant-m|La goutte.
+maman|Oui.
+maman|On nomme le son.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1351,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Blanche entend un bruit. C'est quoi ?</t>
+          <t>Aniss entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1562,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Blanche entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Aniss entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Blanche a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. C'est du bon travail, Aniss. Le chat ronronne. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1735,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Blanche a entendu un son. Elle a dit le nom. Pluie. Train. Chat.</t>
+          <t>narrateur|Aniss a entendu un son.
+narrateur|Il a dit le nom.
+maman|Pluie.
+maman|Train.
+maman|Chat.
+maman|Bravo.
+papa|Tu as nommé le son.
+papa|C'est du bon travail, Aniss.
+enfant-m|Le chat ronronne.
+maman|Oui.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1707,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le chat ronronne. Blanche pose la tête sur maman.</t>
+          <t>Le chat ronronne. Aniss pose la tête sur maman. Tu es au chaud, maintenant. Oui, maman. Les chaussures sèchent près de la porte. La soupe est prête. On y va ? Oui. La flaque a disparu dans le tapis. Le gant attend encore près du paillasson. Tu as nommé le son. Viens, la vapeur sent la carotte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,7 +1908,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le chat ronronne. Blanche pose la tête sur maman.</t>
+          <t>narrateur|Le chat ronronne.
+narrateur|Aniss pose la tête sur maman.
+maman|Tu es au chaud, maintenant.
+enfant-m|Oui, maman.
+papa|Les chaussures sèchent près de la porte.
+papa|La soupe est prête.
+maman|On y va ?
+enfant-m|Oui.
+narrateur|La flaque a disparu dans le tapis.
+narrateur|Le gant attend encore près du paillasson.
+papa|Tu as nommé le son.
+maman|Viens, la vapeur sent la carotte.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1871,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Aniss. Tu as fait du bon travail. La soupe fume encore, tout doucement. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,7 +2087,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai entendu un son.
+enfant-m|J'ai dit le nom.
+maman|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+narrateur|La soupe fume encore, tout doucement.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2033,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ça sent la soupe près de la porte. Les chaussures mouillées font une petite flaque. Le tapis absorbe une goutte. La porte est encore froide. Une vapeur monte de la cuisine. Un manteau goutte sur le crochet. La capuche est lourde, toute sombre. Un gant a glissé près du paillasson. Tes chaussures sont mouillées, Aniss. On les laisse ici. Oui, maman. Elles font une flaque. La soupe est presque prête. Je vous entends d'ici. En ce moment, Aniss s'assoit près de la fenêtre. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Aniss le caresse. Le poil sent un peu la pluie. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Aniss. Tu as dit le nom. C'est du bon travail. Tu as fini d'écouter ? Encore un peu. La soupe attend. Le manteau goutte encore. Une goutte tombe sur le gant. Encore un petit son. La goutte. Oui. On nomme le son.</t>
+          <t>Ça sent la soupe près de la porte. Les chaussures mouillées font une petite flaque. Le tapis absorbe une goutte. La porte est encore froide. Une vapeur monte de la cuisine. Un manteau goutte sur le crochet. La capuche est lourde, toute sombre. Un gant a glissé près du paillasson. Tes chaussures sont mouillées, Aniss. On les laisse ici. Oui, maman. Elles font une flaque. La soupe est presque prête. Je vous entends d'ici. En ce moment, Aniss s'assoit près de la fenêtre. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Aniss le caresse. Le poil sent un peu la pluie. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Aniss. Tu as dit le nom. Tu as fini d'écouter ? Encore un peu. La soupe attend. Le manteau goutte encore. Une goutte tombe sur le gant. Encore un petit son. La goutte. Oui. On nomme le son.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Blanche s'assoit près de la fenêtre. Maman est là. Il pleut. Ça fait plic ploc. Maman dit : c'est un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Quel nom ? Blanche dit : la pluie. Maman dit : oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Maman dit : encore un son. Quel nom ? Blanche dit : le train. Maman dit : oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Maman dit : un son. Quel nom ? Blanche dit : le chat. Le chat vient. Blanche le caresse. Pluie. Train. Chat. On entend. On nomme le son.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ça sent la soupe près de la porte. Les chaussures mouillées font une petite flaque. Le tapis absorbe une goutte. La porte est encore froide. Une vapeur monte de la cuisine. Un manteau goutte sur le crochet. La capuche est lourde, toute sombre. Un gant a glissé près du paillasson. Tes chaussures sont mouillées, Aniss. On les laisse ici. Oui, maman. Elles font une flaque. La soupe est presque prête. Je vous entends d'ici. En ce moment, Aniss s'assoit près de la fenêtre. Il pleut. Ça fait plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Plus loin, un bruit long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Puis, dans la pièce, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. Le chat vient. Aniss le caresse. Le poil sent un peu la pluie. On entend. On nomme le son. Pluie. Train. Chat. Bravo, Aniss. Tu as dit le nom. Tu as fini d'écouter ? Encore un peu. La soupe attend. Le manteau goutte encore. Une goutte tombe sur le gant. Encore un petit son. La goutte. Oui. On nomme le son.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1369,7 +1369,6 @@
 enfant-m|Chat.
 papa|Bravo, Aniss.
 papa|Tu as dit le nom.
-maman|C'est du bon travail.
 maman|Tu as fini d'écouter ?
 enfant-m|Encore un peu.
 papa|La soupe attend.
@@ -1381,7 +1380,6 @@
 maman|On nomme le son.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1411,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Blanche entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1566,7 +1564,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. C'est du bon travail, Aniss. Le chat ronronne. Oui.</t>
+          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat ronronne. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Blanche a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Elle a dit le nom. Pluie. Train. Chat.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a entendu un son. Il a dit le nom. Pluie. Train. Chat. Bravo. Tu as nommé le son. Le chat ronronne. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,12 +1739,10 @@
 maman|Chat.
 maman|Bravo.
 papa|Tu as nommé le son.
-papa|C'est du bon travail, Aniss.
 enfant-m|Le chat ronronne.
 maman|Oui.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,7 +1772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le chat ronronne. Blanche pose la tête sur maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chat ronronne. Aniss pose la tête sur maman. Tu es au chaud, maintenant. Oui, maman. Les chaussures sèchent près de la porte. La soupe est prête. On y va ? Oui. La flaque a disparu dans le tapis. Le gant attend encore près du paillasson. Tu as nommé le son. Viens, la vapeur sent la carotte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,7 +1917,6 @@
 maman|Viens, la vapeur sent la carotte.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1947,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Aniss. Tu as fait du bon travail. La soupe fume encore, tout doucement. L'histoire est finie.</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Aniss. La soupe fume encore, tout doucement.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai entendu un son. J'ai dit le nom. Bravo, Aniss. La soupe fume encore, tout doucement.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,12 +2084,9 @@
           <t>enfant-m|J'ai entendu un son.
 enfant-m|J'ai dit le nom.
 maman|Bravo, Aniss.
-papa|Tu as fait du bon travail.
-narrateur|La soupe fume encore, tout doucement.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La soupe fume encore, tout doucement.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2114,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2150,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-05.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blanche, maman</t>
+          <t>Aniss, maman, papa</t>
         </is>
       </c>
     </row>
